--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00750B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00750B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C05CD7DB-3A79-477D-A610-9C3166B29146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04ECBBCC-6744-4347-9E9E-BA68CD05037F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{885D4B57-FBD9-400F-8596-5E6DE4C6BC52}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{4EED1619-B84A-4F46-BC20-AC16CE69DF68}"/>
   </bookViews>
   <sheets>
     <sheet name="00750B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1609,25 +1609,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897FE12-DE96-422C-AD89-7336D3FDA1C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD525A1-2023-4F4B-BB9B-7ADAE6991827}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1685,7 +1685,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1781,7 +1781,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1861,7 +1861,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>27</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51" t="s">
         <v>74</v>
       </c>
